--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="503">
   <si>
     <t>Filename</t>
   </si>
@@ -808,691 +808,721 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9269,0.0541,0.0024,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.9849,0.0001,0.0001,0.0147</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.0025,0.9989</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,1,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.9849,0.0032,0.0021,0.0012</t>
+  </si>
+  <si>
+    <t>0.0055,0.0000,0.0000,0.9993</t>
+  </si>
+  <si>
+    <t>0.9740,0.0002,0.0001,0.0319</t>
+  </si>
+  <si>
+    <t>0.0024,0.0001,0.0024,0.9979</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0011,0.0001,0.0002</t>
+  </si>
+  <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
+    <t>0.9789,0.0026,0.0058,0.0001</t>
+  </si>
+  <si>
+    <t>0.0041,0.0166,0.9859,0.0025</t>
+  </si>
+  <si>
+    <t>0.0325,0.0072,0.9605,0.0003</t>
+  </si>
+  <si>
+    <t>0.0012,0.0003,0.9979,0.0005</t>
+  </si>
+  <si>
+    <t>0.5474,0.0104,0.3809,0.0052</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9972,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0041,0.9922,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.0019,0.9958,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9842,0.0012,0.0044,0.0001</t>
+  </si>
+  <si>
+    <t>0.5326,0.0032,0.5370,0.0005</t>
+  </si>
+  <si>
+    <t>0.0058,0.0002,0.9948,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0005,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.0112,0.0002,0.9928,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.3160,0.7192,0.0013,0.0019</t>
+  </si>
+  <si>
+    <t>0.1368,0.0259,0.7990,0.0014</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9988,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.7373,0.0011,0.2893,0.0006</t>
+  </si>
+  <si>
+    <t>0.9318,0.1145,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.9988,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.8319,0.9231,0.0010</t>
+  </si>
+  <si>
+    <t>0.0006,0.0006,0.9981,0.0007</t>
+  </si>
+  <si>
+    <t>0.0029,0.0155,0.9907,0.0001</t>
+  </si>
+  <si>
+    <t>0.0262,0.0004,0.9788,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.8513,0.9905,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9969,0.0085,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0017,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0054,0.0028,0.0004,0.9960</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9988,0.0111,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0620,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.2975,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.0001,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0090,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0008,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9941,0.0019,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0013,0.9999,0.0004</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0022,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9774,0.9966,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0039,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0008,0.9992,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.9886,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9988,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9449,0.0013,0.0654,0.0001</t>
+  </si>
+  <si>
+    <t>0.5991,0.0481,0.2063,0.0011</t>
+  </si>
+  <si>
+    <t>0.0002,0.0022,0.9997,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9914,0.9869,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9937,0.9876,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.0159,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9467,0.9958,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.8889,0.7586</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.0029,0.9990</t>
+  </si>
+  <si>
+    <t>0.0059,0.0001,0.0025,0.9935</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0037,0.9993</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.1428,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9943,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9550,0.9323,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9586,0.9723,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9940,0.8225,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.9604,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0019,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0032,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0011,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.0003,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.9874,0.0004,0.0060,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9981,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0178,0.9686,0.0093,0.0010</t>
+  </si>
+  <si>
+    <t>0.0036,0.9911,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.2269,0.8236,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.6268,0.0239,0.2277,0.0066</t>
+  </si>
+  <si>
+    <t>0.0494,0.0026,0.9448,0.0018</t>
+  </si>
+  <si>
+    <t>0.9242,0.0203,0.0109,0.0031</t>
+  </si>
+  <si>
+    <t>0.5137,0.0078,0.3953,0.0036</t>
+  </si>
+  <si>
+    <t>0.0005,0.0208,0.0014,0.9950</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9976,0.8119,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9979,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.3699,0.6518,0.0106,0.0007</t>
+  </si>
+  <si>
+    <t>0.9634,0.0466,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0013,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9806,0.9640,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9489,0.9966,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0884,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.0121,0.9944,0.0002</t>
+  </si>
+  <si>
+    <t>0.9927,0.0005,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.5956,0.0024,0.0817,0.1192</t>
+  </si>
+  <si>
+    <t>0.0143,0.0002,0.9922,0.0000</t>
+  </si>
+  <si>
+    <t>0.9741,0.0024,0.0072,0.0002</t>
+  </si>
+  <si>
+    <t>0.0132,0.0001,0.0002,0.9964</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0003,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0009,0.9999</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.0056,0.9982</t>
+  </si>
+  <si>
+    <t>0.0000,0.9945,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0229,0.9681,0.0037,0.0021</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.3295,0.6542,0.0132,0.0009</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9255,0.0031,0.0010,0.0547</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0829,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.9414,0.0002,0.0066,0.0226</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.6717,0.3770,0.0039,0.0003</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9876,0.0025,0.0028,0.0004</t>
+  </si>
+  <si>
+    <t>0.7197,0.0308,0.1041,0.0023</t>
+  </si>
+  <si>
+    <t>0.9265,0.0186,0.0225,0.0005</t>
+  </si>
+  <si>
+    <t>0.9926,0.0013,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9909,0.0021,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.1186,0.0051,0.8739,0.0013</t>
-  </si>
-  <si>
-    <t>0.0067,0.0142,0.9892,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.0004,0.9969,0.0003</t>
-  </si>
-  <si>
-    <t>0.5356,0.0021,0.4744,0.0028</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9986,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0154,0.9800,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.9987,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.6476,0.0017,0.3901,0.0011</t>
-  </si>
-  <si>
-    <t>0.6934,0.0022,0.3449,0.0007</t>
-  </si>
-  <si>
-    <t>0.0091,0.0019,0.9886,0.0001</t>
-  </si>
-  <si>
-    <t>0.0082,0.0022,0.9857,0.0003</t>
-  </si>
-  <si>
-    <t>0.0025,0.0003,0.9973,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.6258,0.4195,0.0038,0.0009</t>
-  </si>
-  <si>
-    <t>0.4242,0.0932,0.2897,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.9924,0.0102,0.0005</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.6313,0.0007,0.4189,0.0011</t>
-  </si>
-  <si>
-    <t>0.9554,0.0636,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.0011,0.9978,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0030,0.2913,0.9583,0.0015</t>
-  </si>
-  <si>
-    <t>0.0041,0.0007,0.9924,0.0009</t>
-  </si>
-  <si>
-    <t>0.0002,0.0199,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0035,0.0004,0.9945,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.1207,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9965,0.0095,0.0003</t>
-  </si>
-  <si>
-    <t>0.0012,0.0018,0.9974,0.0001</t>
-  </si>
-  <si>
-    <t>0.0108,0.0017,0.0021,0.9899</t>
-  </si>
-  <si>
-    <t>0.0003,0.9982,0.0015,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0833,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.5847,0.9940,0.0000</t>
-  </si>
-  <si>
-    <t>0.0126,0.0006,0.9897,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0001,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0017,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0011,0.9999,0.0000</t>
+    <t>0.9978,0.0008,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0008,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9892,0.0117,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9131,0.1055,0.0048,0.0007</t>
+  </si>
+  <si>
+    <t>0.5806,0.5158,0.0022,0.0006</t>
+  </si>
+  <si>
+    <t>0.9785,0.0106,0.0074,0.0006</t>
+  </si>
+  <si>
+    <t>0.9924,0.0098,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0015,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9807,0.0150,0.0015,0.0011</t>
+  </si>
+  <si>
+    <t>0.0001,0.0182,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9844,0.0059,0.0038,0.0018</t>
+  </si>
+  <si>
+    <t>0.0004,0.5002,0.9958,0.0000</t>
+  </si>
+  <si>
+    <t>0.0778,0.0026,0.9398,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0559,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0048,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.0001,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0226,0.0081,0.9647,0.0007</t>
+  </si>
+  <si>
+    <t>0.0395,0.0023,0.9606,0.0013</t>
+  </si>
+  <si>
+    <t>0.5455,0.0638,0.1593,0.0010</t>
+  </si>
+  <si>
+    <t>0.5489,0.0591,0.2056,0.0003</t>
+  </si>
+  <si>
+    <t>0.0881,0.7154,0.1234,0.0010</t>
+  </si>
+  <si>
+    <t>0.0148,0.0186,0.9631,0.0003</t>
+  </si>
+  <si>
+    <t>0.6780,0.0050,0.2212,0.0040</t>
+  </si>
+  <si>
+    <t>0.7909,0.0047,0.1933,0.0006</t>
+  </si>
+  <si>
+    <t>0.0987,0.9113,0.0028,0.0008</t>
+  </si>
+  <si>
+    <t>0.0029,0.9941,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.2874,0.7461,0.0066,0.0007</t>
+  </si>
+  <si>
+    <t>0.8857,0.2157,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.5995,0.5271,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.6860,0.1224,0.0473,0.0007</t>
+  </si>
+  <si>
+    <t>0.9885,0.0006,0.0045,0.0000</t>
+  </si>
+  <si>
+    <t>0.9407,0.0027,0.0247,0.0024</t>
+  </si>
+  <si>
+    <t>0.1341,0.0714,0.7219,0.0011</t>
+  </si>
+  <si>
+    <t>0.1359,0.0018,0.8915,0.0007</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0103,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0539,0.9965,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.0007,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.8828,0.6176,0.0010</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9703,0.0532,0.0006,0.0002</t>
   </si>
   <si>
     <t>0.9993,0.0002,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9992,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0012,1.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0007,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9770,0.9965,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0034,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.0054,0.9942,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9977,0.9966,0.0000</t>
+    <t>0.9980,0.0017,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0021,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9961,0.0027,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0014,0.0313,0.9966,0.0004</t>
+  </si>
+  <si>
+    <t>0.0959,0.2086,0.6133,0.0018</t>
+  </si>
+  <si>
+    <t>0.9158,0.0059,0.0465,0.0026</t>
+  </si>
+  <si>
+    <t>0.0033,0.0001,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.7659,0.9952,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0002,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0015,0.9973,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9294,0.0018,0.0806,0.0001</t>
-  </si>
-  <si>
-    <t>0.6522,0.0047,0.3450,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.0017,0.9995,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9959,0.9971,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9959,0.9917,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0048,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9860,0.9610,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0972,0.9963</t>
+    <t>0.0027,0.0035,0.9931,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0010,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0039,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0312,0.0019,0.9557,0.0064</t>
+  </si>
+  <si>
+    <t>0.9542,0.0033,0.0241,0.0002</t>
+  </si>
+  <si>
+    <t>0.7574,0.0008,0.2623,0.0014</t>
+  </si>
+  <si>
+    <t>0.9946,0.0004,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0029,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0020,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0015,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0036,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0078,0.0533,0.9611,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0043,0.0353,0.9753,0.0027</t>
+  </si>
+  <si>
+    <t>0.0048,0.0478,0.9704,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.3514,0.0005,0.6606,0.0040</t>
+  </si>
+  <si>
+    <t>0.0384,0.0014,0.9688,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.9051,0.0004,0.0040,0.0851</t>
+  </si>
+  <si>
+    <t>0.0005,0.0003,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0026,0.0001,0.0002,0.9989</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0001,0.0002,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0020,0.0001,0.0006,0.9987</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0027,0.9994</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9971,0.2337,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9936,0.9961,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9427,0.9303,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9763,0.9436,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9822,0.9967,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9944,0.9400,0.0000</t>
-  </si>
-  <si>
-    <t>0.9964,0.0029,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9965,0.0037,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0011,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0020,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0080,0.0027,0.9896,0.0002</t>
-  </si>
-  <si>
-    <t>0.9975,0.0001,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9988,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0151,0.9734,0.0084,0.0007</t>
-  </si>
-  <si>
-    <t>0.0010,0.9969,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4391,0.6893,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.6750,0.0036,0.2692,0.0070</t>
-  </si>
-  <si>
-    <t>0.0081,0.0009,0.9906,0.0009</t>
-  </si>
-  <si>
-    <t>0.6179,0.0058,0.3753,0.0004</t>
-  </si>
-  <si>
-    <t>0.1736,0.2165,0.2736,0.0071</t>
-  </si>
-  <si>
-    <t>0.0003,0.0038,0.0006,0.9986</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9959,0.9494,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9975,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.4765,0.5155,0.0187,0.0006</t>
-  </si>
-  <si>
-    <t>0.9678,0.0198,0.0045,0.0013</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0002,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9953,0.9911,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9573,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0280,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0067,0.9971,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.7353,0.0015,0.2389,0.0051</t>
-  </si>
-  <si>
-    <t>0.0698,0.0003,0.9603,0.0002</t>
-  </si>
-  <si>
-    <t>0.3554,0.0157,0.5712,0.0009</t>
-  </si>
-  <si>
-    <t>0.0122,0.0003,0.0002,0.9968</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0004,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0069,0.9995</t>
-  </si>
-  <si>
-    <t>0.0000,0.9876,0.9932,0.0000</t>
-  </si>
-  <si>
-    <t>0.0623,0.9369,0.0026,0.0012</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9630,0.0380,0.0024,0.0005</t>
-  </si>
-  <si>
-    <t>0.9961,0.0004,0.0010,0.0010</t>
-  </si>
-  <si>
-    <t>0.6207,0.0010,0.0006,0.6074</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0757,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.9908,0.0001,0.0019,0.0033</t>
-  </si>
-  <si>
-    <t>0.9979,0.0001,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.6119,0.4597,0.0031,0.0003</t>
-  </si>
-  <si>
-    <t>0.9986,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9898,0.0027,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.1397,0.4637,0.1386,0.0028</t>
-  </si>
-  <si>
-    <t>0.9859,0.0025,0.0030,0.0002</t>
-  </si>
-  <si>
-    <t>0.9956,0.0011,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0004,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9978,0.0006,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9624,0.0409,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9149,0.1027,0.0041,0.0007</t>
-  </si>
-  <si>
-    <t>0.4677,0.6000,0.0051,0.0009</t>
-  </si>
-  <si>
-    <t>0.4439,0.0159,0.5595,0.0018</t>
-  </si>
-  <si>
-    <t>0.9905,0.0095,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9981,0.0005,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9814,0.0152,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.0066,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9837,0.0087,0.0029,0.0020</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0115,0.9975,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0008,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0049,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0034,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0346,0.0049,0.9548,0.0009</t>
-  </si>
-  <si>
-    <t>0.0139,0.0031,0.9842,0.0003</t>
-  </si>
-  <si>
-    <t>0.0126,0.0153,0.9707,0.0011</t>
-  </si>
-  <si>
-    <t>0.2258,0.1755,0.3000,0.0006</t>
-  </si>
-  <si>
-    <t>0.0393,0.7327,0.1577,0.0016</t>
-  </si>
-  <si>
-    <t>0.2699,0.0541,0.5421,0.0004</t>
-  </si>
-  <si>
-    <t>0.9036,0.0229,0.0121,0.0035</t>
-  </si>
-  <si>
-    <t>0.7188,0.0396,0.1411,0.0008</t>
-  </si>
-  <si>
-    <t>0.0266,0.9661,0.0038,0.0008</t>
-  </si>
-  <si>
-    <t>0.0143,0.9834,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.2491,0.7995,0.0034,0.0004</t>
-  </si>
-  <si>
-    <t>0.9845,0.0245,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9785,0.0362,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.6648,0.0836,0.0802,0.0008</t>
-  </si>
-  <si>
-    <t>0.9577,0.0057,0.0154,0.0001</t>
-  </si>
-  <si>
-    <t>0.8715,0.0014,0.0642,0.0072</t>
-  </si>
-  <si>
-    <t>0.8204,0.0337,0.0944,0.0004</t>
-  </si>
-  <si>
-    <t>0.9508,0.0009,0.0430,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0026,0.0228,0.9902,0.0012</t>
-  </si>
-  <si>
-    <t>0.0420,0.0058,0.9478,0.0003</t>
-  </si>
-  <si>
-    <t>0.0070,0.0059,0.9891,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.1746,0.9928,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0006,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9947,0.0028,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9983,0.0014,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0021,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0009,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0646,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0173,0.8913,0.1597,0.0009</t>
-  </si>
-  <si>
-    <t>0.9899,0.0007,0.0036,0.0010</t>
-  </si>
-  <si>
-    <t>0.0009,0.0005,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0023,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.1932,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0051,0.0007,0.9937,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0074,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0032,0.0004,0.9946,0.0015</t>
-  </si>
-  <si>
-    <t>0.9222,0.0103,0.0353,0.0007</t>
-  </si>
-  <si>
-    <t>0.2780,0.0007,0.7816,0.0008</t>
-  </si>
-  <si>
-    <t>0.9952,0.0002,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0017,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0017,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0014,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1856,0.0428,0.7090,0.0014</t>
-  </si>
-  <si>
-    <t>0.0000,0.0014,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0036,0.6987,0.4530,0.0396</t>
-  </si>
-  <si>
-    <t>0.0133,0.0537,0.9327,0.0010</t>
-  </si>
-  <si>
-    <t>0.0010,0.0002,0.9985,0.0002</t>
-  </si>
-  <si>
-    <t>0.0264,0.0003,0.9289,0.0156</t>
-  </si>
-  <si>
-    <t>0.0060,0.0013,0.9910,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.5836,0.0002,0.0019,0.5986</t>
-  </si>
-  <si>
-    <t>0.0016,0.0010,0.0000,0.9995</t>
-  </si>
-  <si>
-    <t>0.0325,0.0002,0.0027,0.9824</t>
-  </si>
-  <si>
-    <t>0.9739,0.0006,0.0003,0.0180</t>
+    <t>0.6179,0.0009,0.0007,0.5725</t>
   </si>
 </sst>
 </file>
@@ -1878,7 +1908,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1892,7 +1922,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1906,7 +1936,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1920,7 +1950,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1934,7 +1964,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1948,7 +1978,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1962,7 +1992,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1976,7 +2006,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1990,7 +2020,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2004,7 +2034,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2018,7 +2048,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2032,7 +2062,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2046,7 +2076,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2060,7 +2090,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2074,7 +2104,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2088,7 +2118,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2102,7 +2132,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2116,7 +2146,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2130,7 +2160,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2144,7 +2174,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2158,7 +2188,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2172,7 +2202,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2186,7 +2216,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2197,10 +2227,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2214,7 +2244,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2228,7 +2258,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2242,7 +2272,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2256,7 +2286,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2270,7 +2300,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2281,10 +2311,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2295,10 +2325,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2312,7 +2342,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2326,7 +2356,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2340,7 +2370,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2354,7 +2384,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2368,7 +2398,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2382,7 +2412,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2393,10 +2423,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2410,7 +2440,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2424,7 +2454,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2438,7 +2468,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2449,10 +2479,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2466,7 +2496,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2480,7 +2510,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2494,7 +2524,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2508,7 +2538,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2522,7 +2552,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2536,7 +2566,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2550,7 +2580,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2561,10 +2591,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2578,7 +2608,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2592,7 +2622,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2606,7 +2636,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2620,7 +2650,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2634,7 +2664,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2648,7 +2678,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2662,7 +2692,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2676,7 +2706,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2690,7 +2720,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2704,7 +2734,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2718,7 +2748,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2732,7 +2762,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2746,7 +2776,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2760,7 +2790,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2774,7 +2804,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2788,7 +2818,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2802,7 +2832,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2816,7 +2846,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2830,7 +2860,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2844,7 +2874,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2858,7 +2888,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2872,7 +2902,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2886,7 +2916,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2900,7 +2930,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2914,7 +2944,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2925,10 +2955,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2942,7 +2972,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2956,7 +2986,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2970,7 +3000,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2984,7 +3014,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2998,7 +3028,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3012,7 +3042,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3026,7 +3056,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3040,7 +3070,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3054,7 +3084,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3068,7 +3098,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3082,7 +3112,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3096,7 +3126,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3110,7 +3140,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3124,7 +3154,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3138,7 +3168,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3152,7 +3182,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3166,7 +3196,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3180,7 +3210,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3194,7 +3224,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3208,7 +3238,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3222,7 +3252,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3236,7 +3266,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3250,7 +3280,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3264,7 +3294,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>355</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3278,7 +3308,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3292,7 +3322,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>352</v>
+        <v>276</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3306,7 +3336,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3320,7 +3350,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3334,7 +3364,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3348,7 +3378,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3362,7 +3392,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3376,7 +3406,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3390,7 +3420,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3404,7 +3434,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3418,7 +3448,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3432,7 +3462,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3446,7 +3476,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3460,7 +3490,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3474,7 +3504,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3488,7 +3518,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3502,7 +3532,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3516,7 +3546,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3530,7 +3560,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3544,7 +3574,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3558,7 +3588,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>277</v>
+        <v>378</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3572,7 +3602,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3586,7 +3616,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3600,7 +3630,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3614,7 +3644,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3628,7 +3658,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3642,7 +3672,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3656,7 +3686,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3670,7 +3700,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>318</v>
+        <v>386</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3684,7 +3714,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3698,7 +3728,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3712,7 +3742,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3726,7 +3756,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3740,7 +3770,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3754,7 +3784,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3768,7 +3798,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3782,7 +3812,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3796,7 +3826,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3810,7 +3840,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3824,7 +3854,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3838,7 +3868,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3849,10 +3879,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3866,7 +3896,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3880,7 +3910,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>336</v>
+        <v>400</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3894,7 +3924,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3908,7 +3938,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3922,7 +3952,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3936,7 +3966,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3950,7 +3980,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3964,7 +3994,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3975,10 +4005,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3992,7 +4022,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4003,10 +4033,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4020,7 +4050,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4034,7 +4064,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4048,7 +4078,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4062,7 +4092,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4076,7 +4106,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4090,7 +4120,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4104,7 +4134,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4118,7 +4148,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4132,7 +4162,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4146,7 +4176,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4160,7 +4190,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4174,7 +4204,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>270</v>
+        <v>420</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4188,7 +4218,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4202,7 +4232,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>413</v>
+        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4216,7 +4246,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4230,7 +4260,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4244,7 +4274,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>271</v>
+        <v>424</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4258,7 +4288,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>416</v>
+        <v>273</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4272,7 +4302,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4286,7 +4316,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4297,10 +4327,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D175" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4311,10 +4341,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4328,7 +4358,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4342,7 +4372,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4356,7 +4386,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4370,7 +4400,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4384,7 +4414,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4398,7 +4428,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4412,7 +4442,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>427</v>
+        <v>364</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4423,10 +4453,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D184" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4440,7 +4470,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4454,7 +4484,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4468,7 +4498,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4482,7 +4512,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4496,7 +4526,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4510,7 +4540,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4524,7 +4554,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4535,10 +4565,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4552,7 +4582,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4566,7 +4596,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4580,7 +4610,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4594,7 +4624,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4608,7 +4638,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4622,7 +4652,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4636,7 +4666,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4650,7 +4680,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4664,7 +4694,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4675,10 +4705,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D202" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4692,7 +4722,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4706,7 +4736,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4720,7 +4750,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4731,10 +4761,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4745,10 +4775,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4762,7 +4792,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4776,7 +4806,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4790,7 +4820,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4804,7 +4834,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4815,10 +4845,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4832,7 +4862,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4846,7 +4876,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4860,7 +4890,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4874,7 +4904,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4888,7 +4918,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4902,7 +4932,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4916,7 +4946,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4930,7 +4960,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>462</v>
+        <v>323</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4944,7 +4974,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4955,10 +4985,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4972,7 +5002,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4986,7 +5016,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5000,7 +5030,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5011,10 +5041,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5028,7 +5058,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5042,7 +5072,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5056,7 +5086,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>291</v>
+        <v>478</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5070,7 +5100,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5084,7 +5114,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5098,7 +5128,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5109,10 +5139,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5126,7 +5156,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5140,7 +5170,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5154,7 +5184,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>269</v>
+        <v>485</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5168,7 +5198,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>355</v>
+        <v>486</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5182,7 +5212,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5196,7 +5226,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5210,7 +5240,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5224,7 +5254,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5238,7 +5268,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>480</v>
+        <v>321</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5252,7 +5282,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5266,7 +5296,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5277,10 +5307,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5294,7 +5324,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5308,7 +5338,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5322,7 +5352,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5336,7 +5366,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5350,7 +5380,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5361,10 +5391,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5378,7 +5408,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5392,7 +5422,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5406,7 +5436,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>336</v>
+        <v>501</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5420,7 +5450,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>336</v>
+        <v>501</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5431,10 +5461,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D256" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>
